--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A5/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2052" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA00909D-D22D-47A5-8910-AB44088B9332}"/>
+  <xr:revisionPtr revIDLastSave="2072" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6973372-CEB3-4FCD-AD97-3714B0956C15}"/>
   <bookViews>
-    <workbookView xWindow="13956" yWindow="1560" windowWidth="10032" windowHeight="10404" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14664" yWindow="2388" windowWidth="8376" windowHeight="9852" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="110">
   <si>
     <t>Market</t>
   </si>
@@ -361,6 +361,12 @@
   </si>
   <si>
     <t>-1.26, 59.92, 41.34</t>
+  </si>
+  <si>
+    <t>17.89, 19.25, 62.86</t>
+  </si>
+  <si>
+    <t>-1.33, 59.85, 41.48</t>
   </si>
 </sst>
 </file>
@@ -486,10 +492,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -789,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F335"/>
+  <dimension ref="A1:F342"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -6429,6 +6431,13 @@
         <v>1</v>
       </c>
       <c r="C330" s="10"/>
+      <c r="D330" s="10">
+        <v>45961</v>
+      </c>
+      <c r="E330" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F330" s="10"/>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="6">
@@ -6441,6 +6450,16 @@
         <f>B331/B335</f>
         <v>0.5313527025615653</v>
       </c>
+      <c r="D331" s="6">
+        <v>2</v>
+      </c>
+      <c r="E331" s="8">
+        <v>3444295</v>
+      </c>
+      <c r="F331" s="7">
+        <f>E331/E335</f>
+        <v>0.54138003934257195</v>
+      </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="6">
@@ -6453,6 +6472,16 @@
         <f>B332/B335</f>
         <v>0.31117670691609672</v>
       </c>
+      <c r="D332" s="6">
+        <v>3</v>
+      </c>
+      <c r="E332" s="8">
+        <v>1978800</v>
+      </c>
+      <c r="F332" s="7">
+        <f>E332/E335</f>
+        <v>0.311031088176559</v>
+      </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="6">
@@ -6465,6 +6494,16 @@
         <f>B333/B335</f>
         <v>0.13144098245303745</v>
       </c>
+      <c r="D333" s="6">
+        <v>4</v>
+      </c>
+      <c r="E333" s="8">
+        <v>770220</v>
+      </c>
+      <c r="F333" s="7">
+        <f>E333/E335</f>
+        <v>0.12106446570413852</v>
+      </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="6">
@@ -6476,6 +6515,16 @@
       <c r="C334" s="7">
         <f>B334/B335</f>
         <v>2.6029608069300478E-2</v>
+      </c>
+      <c r="D334" s="6">
+        <v>1</v>
+      </c>
+      <c r="E334" s="8">
+        <v>168750</v>
+      </c>
+      <c r="F334" s="7">
+        <f>E334/E335</f>
+        <v>2.652440677673051E-2</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -6485,6 +6534,81 @@
       </c>
       <c r="C335" s="7">
         <f>SUM(C331:C334)</f>
+        <v>1</v>
+      </c>
+      <c r="E335" s="9">
+        <f>SUM(E331:E334)</f>
+        <v>6362065</v>
+      </c>
+      <c r="F335" s="7">
+        <f>SUM(F331:F334)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="10">
+        <v>45989</v>
+      </c>
+      <c r="B337" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C337" s="10"/>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="6">
+        <v>2</v>
+      </c>
+      <c r="B338" s="8">
+        <v>3419165</v>
+      </c>
+      <c r="C338" s="7">
+        <f>B338/B342</f>
+        <v>0.55751239830455279</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="6">
+        <v>3</v>
+      </c>
+      <c r="B339" s="8">
+        <v>1883090</v>
+      </c>
+      <c r="C339" s="7">
+        <f>B339/B342</f>
+        <v>0.30704748736118914</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="6">
+        <v>4</v>
+      </c>
+      <c r="B340" s="8">
+        <v>676780</v>
+      </c>
+      <c r="C340" s="7">
+        <f>B340/B342</f>
+        <v>0.11035245181924687</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="6">
+        <v>1</v>
+      </c>
+      <c r="B341" s="8">
+        <v>153860</v>
+      </c>
+      <c r="C341" s="7">
+        <f>B341/B342</f>
+        <v>2.5087662515011263E-2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="B342" s="9">
+        <f>SUM(B338:B341)</f>
+        <v>6132895</v>
+      </c>
+      <c r="C342" s="7">
+        <f>SUM(C338:C341)</f>
         <v>1</v>
       </c>
     </row>
@@ -6495,7 +6619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -6524,7 +6648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="72">
+    <row r="2" spans="1:6" ht="57.6">
       <c r="A2" s="2">
         <v>44946</v>
       </c>
@@ -7028,7 +7152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="57.6">
+    <row r="38" spans="1:6" ht="43.2">
       <c r="A38" s="2">
         <v>45093</v>
       </c>
@@ -7084,7 +7208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="57.6">
+    <row r="42" spans="1:6" ht="43.2">
       <c r="A42" s="2">
         <v>45107</v>
       </c>
@@ -7140,7 +7264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="57.6">
+    <row r="46" spans="1:6" ht="43.2">
       <c r="A46" s="2">
         <v>45121</v>
       </c>
@@ -7196,7 +7320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="57.6">
+    <row r="50" spans="1:6" ht="43.2">
       <c r="A50" s="2">
         <v>45134</v>
       </c>
@@ -7252,7 +7376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="57.6">
+    <row r="54" spans="1:6" ht="43.2">
       <c r="A54" s="2">
         <v>45156</v>
       </c>
@@ -7308,7 +7432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="57.6">
+    <row r="58" spans="1:6" ht="43.2">
       <c r="A58" s="2">
         <v>45170</v>
       </c>
@@ -7364,7 +7488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="57.6">
+    <row r="62" spans="1:6" ht="43.2">
       <c r="A62" s="2">
         <v>45184</v>
       </c>
@@ -7420,7 +7544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="57.6">
+    <row r="66" spans="1:6" ht="43.2">
       <c r="A66" s="2">
         <v>45198</v>
       </c>
@@ -7476,7 +7600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="57.6">
+    <row r="70" spans="1:6" ht="43.2">
       <c r="A70" s="2">
         <v>45211</v>
       </c>
@@ -7532,7 +7656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="57.6">
+    <row r="74" spans="1:6" ht="43.2">
       <c r="A74" s="2">
         <v>45247</v>
       </c>
@@ -7700,7 +7824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="57.6">
+    <row r="86" spans="1:6" ht="43.2">
       <c r="A86" s="2">
         <v>45443</v>
       </c>
@@ -7756,7 +7880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="57.6">
+    <row r="90" spans="1:6" ht="43.2">
       <c r="A90" s="2">
         <v>45457</v>
       </c>
@@ -7812,7 +7936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="57.6">
+    <row r="94" spans="1:6" ht="43.2">
       <c r="A94" s="2">
         <v>45471</v>
       </c>
@@ -7868,7 +7992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="57.6">
+    <row r="98" spans="1:6" ht="43.2">
       <c r="A98" s="2">
         <v>45499</v>
       </c>
@@ -7924,7 +8048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="57.6">
+    <row r="102" spans="1:6" ht="43.2">
       <c r="A102" s="2">
         <v>45527</v>
       </c>
@@ -7980,7 +8104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="57.6">
+    <row r="106" spans="1:6" ht="43.2">
       <c r="A106" s="2">
         <v>45541</v>
       </c>
@@ -8036,7 +8160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="72">
+    <row r="110" spans="1:6" ht="43.2">
       <c r="A110" s="2">
         <v>45555</v>
       </c>
@@ -8092,7 +8216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="72">
+    <row r="114" spans="1:6" ht="43.2">
       <c r="A114" s="2">
         <v>45569</v>
       </c>
@@ -8148,7 +8272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="72">
+    <row r="118" spans="1:6" ht="43.2">
       <c r="A118" s="2">
         <v>45583</v>
       </c>
@@ -8204,7 +8328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="72">
+    <row r="122" spans="1:6" ht="43.2">
       <c r="A122" s="2">
         <v>45604</v>
       </c>
@@ -8596,7 +8720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="57.6">
+    <row r="150" spans="1:6" ht="43.2">
       <c r="A150" s="2">
         <v>45856</v>
       </c>
@@ -8652,7 +8776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="57.6">
+    <row r="154" spans="1:6" ht="43.2">
       <c r="A154" s="2">
         <v>45877</v>
       </c>
@@ -8744,7 +8868,7 @@
         <v>10740580</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:6">
       <c r="A161" s="1" t="s">
         <v>2</v>
       </c>
@@ -8754,8 +8878,17 @@
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" ht="57.6">
+      <c r="D161" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="43.2">
       <c r="A162" s="2">
         <v>45926</v>
       </c>
@@ -8765,14 +8898,61 @@
       <c r="C162" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="D162" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="5"/>
       <c r="B163" s="4">
         <v>-951000</v>
       </c>
       <c r="C163" s="13">
         <v>10740580</v>
+      </c>
+      <c r="D163" s="5"/>
+      <c r="E163" s="4">
+        <v>-948000</v>
+      </c>
+      <c r="F163" s="13">
+        <v>10770840</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="43.2">
+      <c r="A166" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="5"/>
+      <c r="B167" s="4">
+        <v>-948000</v>
+      </c>
+      <c r="C167" s="13">
+        <v>10770840</v>
       </c>
     </row>
   </sheetData>
